--- a/data/seed/portfolio/L-2025-4118/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-4118/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,26 +542,26 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>6411000</v>
+        <v>3256000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bekobod Mato XK</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>216391139</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000928099241001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -570,122 +570,122 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>149111000</v>
+        <v>145956000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46208</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>23600000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>13171000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4118)</t>
+          <t>Denov Metall Servis XK</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16307000357876854417</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4118 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по счет-фактуре №5156 за поставленный товар</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>125511000</v>
+        <v>159127000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>2503000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>2411000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish AJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>271750547</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000141629067001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №43/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №45/26 от 03.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>128014000</v>
+        <v>156716000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>1532000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>387415652</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4118)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>16307000357876854417</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6657 06.07.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-4118 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>129546000</v>
+        <v>133116000</v>
       </c>
     </row>
     <row r="12">
@@ -695,32 +695,37 @@
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>13204000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>13871000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Barakali Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата по счет-фактуре №6438 за поставленный товар</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>116342000</v>
+        <v>146987000</v>
       </c>
     </row>
     <row r="13">
@@ -730,343 +735,338 @@
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>14024000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>5375000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ishonch Savdo MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>314776529</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000380639285001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №74/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №43/26, QQS 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>102318000</v>
+        <v>152362000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1472000</v>
+        <v>1795000</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saodat Qurilish Materiallari AJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>319021810</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000591779878001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №89/24</t>
+          <t>Оплата за сырье по дог. №31/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>100846000</v>
+        <v>150567000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>4698000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>13204000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>387415652</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8599 от 08.07.2026, в т.ч. НДС 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>105544000</v>
+        <v>137363000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>4072000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>53278000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Omad Agro MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>358238658</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000701734430001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2605 08.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно с/ф №2104</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>109616000</v>
+        <v>84085000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>2971000</v>
+        <v>5638000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6017 от 08.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №3127 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>112587000</v>
+        <v>89723000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>4630000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>1472000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Termiz Agro Servis MChJ</t>
+          <t>Mehnat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>254282643</t>
+          <t>247765290</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000778128919001</t>
+          <t>20208000806392850001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №234/26, НДС 12%</t>
+          <t>Арендная плата за июль 2026 г. по договору №93/21</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>117217000</v>
+        <v>88251000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>22278000</v>
+        <v>9395000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Lazzat Tekstil AJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>235008991</t>
+          <t>395020603</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000299291143001</t>
+          <t>20208000998093109001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №179/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №3904</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>94939000</v>
+        <v>78856000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>3177000</v>
+        <v>5005000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5963 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №8599 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>98116000</v>
+        <v>83861000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>5015000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>2765000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1076,437 +1076,437 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №184/26</t>
+          <t>Оплата по с/ф №9714 за поставленный товар</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>93101000</v>
+        <v>86626000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>3051000</v>
+        <v>2531000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Shartnoma №179/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2605 08.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>96152000</v>
+        <v>89157000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>19194000</v>
+        <v>2749000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bunyodkor Agro MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>339582386</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000827017344001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8330</t>
+          <t>Предоплата за материалы по договору №177/26</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76958000</v>
+        <v>86408000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>8602000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IYUN OYI UCHUN IJTIMOIY SOLIQ</t>
+          <t>Оплата по с/ф №8346 за поставленный товар</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>75158000</v>
+        <v>95010000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>5770000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Mato MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>228264367</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000812891949001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad soli'i iyun 2026</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №234/26, НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>73358000</v>
+        <v>100780000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>2135000</v>
+        <v>3792000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №736 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №130/26 от 09.07.2026</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>75493000</v>
+        <v>104572000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>2007000</v>
+        <v>3318000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Qarshi Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>219709254</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000467013464001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Shartnoma №261/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №2722 за поставленный товар</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>77500000</v>
+        <v>107890000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>1508000</v>
+        <v>5938000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Qarshi Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>219709254</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000467013464001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2632 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №5963 за поставленный товар</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>79008000</v>
+        <v>113828000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>1452000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>2971000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Xiva Metall Servis XK</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>348026229</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000038580082001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №55/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №8635</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>80460000</v>
+        <v>110857000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>6143000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>2634000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bunyodkor Agro MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>339582386</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000827017344001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №235/26 от 15.07.2026, НДС 12%</t>
+          <t>Shartnoma №179/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>74317000</v>
+        <v>113491000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>2193000</v>
+        <v>1962000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bekobod Mato XK</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>216391139</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000928099241001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №271/26 от 17.07.2026</t>
+          <t>Оплата за товар по с/ф №729 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>76510000</v>
+        <v>115453000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>1874000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>2108000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Yangi Hayot Poligraf XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>371671734</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000910587057001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,237 +1516,237 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №55/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №250/26</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>78384000</v>
+        <v>113345000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>10487000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>2764000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Omad Agro MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>358238658</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000701734430001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3065 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3569</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>88871000</v>
+        <v>110581000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>8531000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>8543000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8032 20.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №200/26</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>97402000</v>
+        <v>102038000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>2769000</v>
+        <v>12864000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2201 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №13/26, QQS 12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>100171000</v>
+        <v>114902000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>12656000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>12237000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7166</t>
+          <t>Shartnoma №261/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>87515000</v>
+        <v>127139000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>2443000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>7249000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №736 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>85072000</v>
+        <v>134388000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>32501000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>3559000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Chirchiq Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>302622930</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000858008241001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1756,672 +1756,677 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №114/26 от 21.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №55/26, НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>52571000</v>
+        <v>137947000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>4568000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5315 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>57139000</v>
+        <v>136147000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>8041000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Termiz Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>276860246</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000394697352001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>65180000</v>
+        <v>134347000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46226</v>
+        <v>46219</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>920000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>2889000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000087743622001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товар по счет-фактуре №9809 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>64260000</v>
+        <v>137236000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>7353000</v>
+        <v>3662000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish AJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>271750547</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000141629067001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №274/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №55/26, НДС 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>71613000</v>
+        <v>140898000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>6838000</v>
+        <v>2233000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun tolov, shartnoma №208/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №113/26, QQS 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>78451000</v>
+        <v>143131000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>1969000</v>
+        <v>1913000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №171/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №271/26 от 17.07.2026</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>80420000</v>
+        <v>145044000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5668000</v>
+        <v>2730000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата а материалы по договору №222/26</t>
+          <t>Оплата за транспортные услуги по дог. №236/26</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>74752000</v>
+        <v>142314000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>100580000</v>
+        <v>19908000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №193/26 от 27.07.2026</t>
+          <t>Оплата по счет-фактуре №2201 за поставленный товар</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>175332000</v>
+        <v>162222000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>3278000</v>
+        <v>4365000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №6377 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Shartnoma №76/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>178610000</v>
+        <v>166587000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>10966000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>2468000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>235008991</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000299291143001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №102</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8032 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>167644000</v>
+        <v>169055000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>1590000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>2824000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9629 за поставленный товар</t>
+          <t>Оплата за товары согласно с/ф №2139</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>169234000</v>
+        <v>166231000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>3341000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>2847000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №94/26 от 30.07.2026</t>
+          <t>Оплата за сырье по договору №141/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>172575000</v>
+        <v>163384000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>5323000</v>
+        <v>8894000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>235008991</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000299291143001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9104</t>
+          <t>Оплата за сырье по дог. №64/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>167252000</v>
+        <v>154490000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46233</v>
+        <v>46224</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>11630000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>2742000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4308</t>
+          <t>Оплата за товар по счет-фактуре №4812 от 21.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>155622000</v>
+        <v>157232000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>300000</v>
+        <v>3989000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Oydin Plastik XK</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВАНИЕ</t>
+          <t>Оплата за товары согласно с/ф №589</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>155322000</v>
+        <v>153243000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>12792000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>8839000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ziyo Sut Mahsulotlari MChJ</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>276018511</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000766124533001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №6384</t>
+          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>142530000</v>
+        <v>162082000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>9453000</v>
+        <v>2000000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guliston Agro MChJ</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>347392767</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000366955723001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2431,277 +2436,277 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6630</t>
+          <t>Mahsulot uchun to'lov, shartnoma №281/26, QQS 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>151983000</v>
+        <v>164082000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>3707000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>920000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000814682149001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3265 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>155690000</v>
+        <v>163162000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>1919000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>2482000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №90/26 от 03.08.2026</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>157609000</v>
+        <v>160680000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>8821000</v>
+        <v>4098000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Qarshi Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>219709254</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000467013464001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №101/26 от 04.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №171/26, QQS 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>166430000</v>
+        <v>164778000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>9105000</v>
+        <v>2029000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>235008991</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000299291143001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №233</t>
+          <t>Предоплата за материалы по дог. №23/26</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>157325000</v>
+        <v>162749000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>10392000</v>
+        <v>2882000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №298/26</t>
+          <t>Оплата за сырье по договору №178/26 от 24.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>146933000</v>
+        <v>159867000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>23937000</v>
+        <v>3245000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №117/26</t>
+          <t>Оплата за сырье по дог. №127/26 от 24.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>122996000</v>
+        <v>156622000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>2424000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>34141000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Yangi Hayot Poligraf XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>371671734</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000910587057001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2711,427 +2716,432 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №118/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №7268</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>125420000</v>
+        <v>122481000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>12901000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>4033000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Barakali Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №5355</t>
+          <t>Оплата по счет-фактуре №9549 за поставленный товар</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>112519000</v>
+        <v>126514000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>23600000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>3482000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4118)</t>
+          <t>Denov Metall Servis XK</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>16307000357876854417</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4118 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по с/ф №9784 за поставленный товар</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>88919000</v>
+        <v>129996000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>18725000</v>
+        <v>2430000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата по счетфактуре №9732 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №285/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>107644000</v>
+        <v>132426000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>3357000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>2429000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №292/26</t>
+          <t>ОПЛАТА ПО С/Ф №6377 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>104287000</v>
+        <v>134855000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>10526000</v>
+        <v>2491000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №3181 ОТ 10.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №49/26 от 28.07.2026</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>114813000</v>
+        <v>137346000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>2117000</v>
+        <v>2350000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7415 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №3120 за поставленный товар</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>116930000</v>
+        <v>139696000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>1832000</v>
+        <v>8761000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №157/26 от 10.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №9135 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>118762000</v>
+        <v>148457000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>1438000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>4286000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saodat Qurilish Materiallari AJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>319021810</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000591779878001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №89/24</t>
+          <t>Оплата за товар по с/ф №6017 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>117324000</v>
+        <v>152743000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>3440000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>1921000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №192/26</t>
+          <t>Оплата по счет-фактуре №9629 за поставленный товар</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>113884000</v>
+        <v>154664000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>4877000</v>
+        <v>3450000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Omad Agro MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>358238658</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000701734430001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №132/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №2336</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>109007000</v>
+        <v>151214000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46245</v>
+        <v>46234</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>13953000</v>
+        <v>300000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ishonch Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>314776529</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000380639285001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3141,237 +3151,237 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №122/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>95054000</v>
+        <v>150914000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46245</v>
+        <v>46234</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>24744000</v>
+        <v>1716000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7310</t>
+          <t>Оплата за сырье по договору №136/26 от 31.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>70310000</v>
+        <v>149198000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46248</v>
+        <v>46234</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>8743000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>3315000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish AJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>271750547</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000141629067001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №925 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, sartnoma №22/26</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>79053000</v>
+        <v>145883000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46248</v>
+        <v>46237</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>1875000</v>
+        <v>10241000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6918 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №8371 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>80928000</v>
+        <v>156124000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>6573000</v>
+        <v>3892000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish AJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>271750547</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000141629067001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №193/26 от 17.08.2026</t>
+          <t>Предоплата за товар по дог. №214/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>87501000</v>
+        <v>160016000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>5904000</v>
+        <v>1282000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3039 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №2902 за поставленный товар</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>93405000</v>
+        <v>161298000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46251</v>
+        <v>46238</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>4402000</v>
+        <v>4452000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,237 +3391,227 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №171/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №46/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>97807000</v>
+        <v>165750000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46251</v>
+        <v>46238</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>1937000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>3903000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Omad Agro MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>358238658</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000701734430001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №94/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1463</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>99744000</v>
+        <v>161847000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46251</v>
+        <v>46238</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>1456000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>12901000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>294197092</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3757 за поставленный товар</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>101200000</v>
+        <v>148946000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>1759000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>1652000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА ИЮЛЬ 2026 Г.</t>
+          <t>Оплата за товар по счет-фактуре №9617 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>99441000</v>
+        <v>150598000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>1759000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>1624000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5183 05.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>97682000</v>
+        <v>152222000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46239</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>4963000</v>
+        <v>23600000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>217610019</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4118)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>16307000357876854417</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3837</t>
+          <t>Kredit shartnomasi L-2025-4118 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>92719000</v>
+        <v>128622000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46253</v>
+        <v>46240</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>6079000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>28939000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Chirchiq Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>302622930</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000858008241001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3621,77 +3621,77 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №7389</t>
+          <t>Оплата по с/ф №7407 за поставленный товар</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>86640000</v>
+        <v>157561000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46254</v>
+        <v>46241</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>14787000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>19167000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shodlik Yog' Zavodi AJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>335966150</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000634290403001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №223/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3519</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>71853000</v>
+        <v>176728000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46255</v>
+        <v>46241</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>13017000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>2297000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3701,37 +3701,37 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №4/26</t>
+          <t>Предоплата за товар по дог. №114/26 от 07.08.2026</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>58836000</v>
+        <v>179025000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46258</v>
+        <v>46241</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>10185000</v>
+        <v>1506000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Mato MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>228264367</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000812891949001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3741,117 +3741,117 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №279/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3641</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>69021000</v>
+        <v>180531000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>7115000</v>
+        <v>20982000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №251/26 от 24.08.2026</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8895 ОТ 10.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>76136000</v>
+        <v>201513000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>5100000</v>
+        <v>5010000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1634 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата по счет-фактуре №5328 за поставленный товар</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>81236000</v>
+        <v>206523000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>1949000</v>
+        <v>1202000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3861,397 +3861,397 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8155 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №134/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>83185000</v>
+        <v>207725000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>1725000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>1438000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Mehnat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>247765290</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000806392850001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1728 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Аренда помещения за август, дог. №93/21</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>84910000</v>
+        <v>206287000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>1664000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>1932000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №236/26 от 24.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №199/26</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>86574000</v>
+        <v>204355000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>2442000</v>
+        <v>1985000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №1446</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>84132000</v>
+        <v>202370000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>4896000</v>
+        <v>42018000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №5854</t>
+          <t>Предоплата за материалы по договору №215/26</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>79236000</v>
+        <v>160352000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46261</v>
+        <v>46245</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>2039000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>6685000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bog'ishamol Trans Servis MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>310010115</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000377800474001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6242 от 27.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №201/26</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>81275000</v>
+        <v>153667000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46261</v>
+        <v>46247</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>899000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>898000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000087743622001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товар по счет-фактуре №1553 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>80376000</v>
+        <v>154565000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>42797000</v>
+        <v>26393000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №78/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8054 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>123173000</v>
+        <v>180958000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>30516000</v>
+        <v>5416000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №471</t>
+          <t>Shartnoma №164/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>153689000</v>
+        <v>186374000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>3176000</v>
+        <v>3808000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №56/26 от 31.08.2026</t>
+          <t>Shartnoma №28/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>156865000</v>
+        <v>190182000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>3012000</v>
+        <v>3157000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4261,312 +4261,317 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №127/26, QQS 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №4348 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>159877000</v>
+        <v>193339000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>2099000</v>
+        <v>1555000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Denov Yog'och XK</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>220309514</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000994887299001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7786 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №275/26, НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>161976000</v>
+        <v>194894000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>1746000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>1759000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №945 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>163722000</v>
+        <v>193135000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>300000</v>
+        <v>1759000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>163422000</v>
+        <v>191376000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>5248000</v>
+        <v>2136000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Omad Agro MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>358238658</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000701734430001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4019</t>
+          <t>Tovarlar uchun to'lov h/f №7213</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>158174000</v>
+        <v>189240000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>7785000</v>
+        <v>62041000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №284/26 ОТ 31.08.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №145/26</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>150389000</v>
+        <v>127199000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46252</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>9003000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>1807000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №81/26</t>
+          <t>Предоплата за товар по дог. №70/26 о 18.08.2026</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>141386000</v>
+        <v>129006000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46266</v>
+        <v>46253</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>19405000</v>
+        <v>1122000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2343 от 01.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по до. №67/26, НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>160791000</v>
+        <v>130128000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46267</v>
+        <v>46254</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>22441000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>3581000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish AJ</t>
+          <t>Afrosiyob Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>271750547</t>
+          <t>339276793</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000141629067001</t>
+          <t>20208000695572322001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4576,512 +4581,517 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6999 02.09.2026, QQS BILAN</t>
+          <t>Оплата за товары согласно с/ф №9898</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>183232000</v>
+        <v>126547000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46267</v>
+        <v>46255</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>18814000</v>
+        <v>931000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №278/26 от 02.09.2026</t>
+          <t>Оплата за продукцию по дог. №215/26, НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>202046000</v>
+        <v>127478000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46267</v>
+        <v>46255</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>2706000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>2388000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5675 от 02.09.2026, в т.ч. НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>204752000</v>
+        <v>125090000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46267</v>
+        <v>46258</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>1818000</v>
+        <v>15259000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1460 от 02.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №237/26, НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>206570000</v>
+        <v>140349000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46267</v>
+        <v>46258</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>3632000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>954000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №214/26</t>
+          <t>Оплата за товар по счет-фактуре №6693 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>202938000</v>
+        <v>141303000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46268</v>
+        <v>46258</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>3336000</v>
+        <v>7583000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №72/26 от 03.09.2026, НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №9205</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>199602000</v>
+        <v>133720000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46268</v>
+        <v>46258</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>4739000</v>
+        <v>9113000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Shodlik Yog' Zavodi AJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>335966150</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000634290403001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №34/26</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №52/26 ОТ 24.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>194863000</v>
+        <v>124607000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46269</v>
+        <v>46258</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>1936000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>16526000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Tur Servis AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>391515743</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000948597057001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №275/26 от 04.09.2026</t>
+          <t>Оплата за транспортные услуги по дог. №194/26</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>196799000</v>
+        <v>108081000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46270</v>
+        <v>46260</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>23600000</v>
+        <v>899000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4118)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>16307000357876854417</t>
+          <t>20208000814682149001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4118 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>173199000</v>
+        <v>107182000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>6402000</v>
+        <v>27851000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №266/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №221/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>179601000</v>
+        <v>135033000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>5785000</v>
+        <v>3613000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №212/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1847 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>185386000</v>
+        <v>138646000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>5714000</v>
+        <v>1548000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №414 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №4703 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>191100000</v>
+        <v>140194000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>1980000</v>
+        <v>930000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Shahrisabz Yog'och MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>284144977</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000981391168001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SHARTNOMA №12/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Предоплата за товар по договору №184/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>193080000</v>
+        <v>141124000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>5182000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>836000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5091,72 +5101,72 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3641</t>
+          <t>Оплата за товар по с/ф №7860 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>187898000</v>
+        <v>141960000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>12971000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>706000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Barakali Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Предоплата за товар по договору №71/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>174927000</v>
+        <v>142666000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>1446000</v>
+        <v>300000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Saodat Qurilish Materiallari AJ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>319021810</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000591779878001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5166,197 +5176,197 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>173481000</v>
+        <v>142366000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>2230000</v>
+        <v>1961000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №271/26 от 08.09.2026, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №278/26</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>171251000</v>
+        <v>140405000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46273</v>
+        <v>46266</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>4090000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>4564000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №78/26</t>
+          <t>Предоплата за товар по дог. №91/26 от 01.09.2026</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>167161000</v>
+        <v>144969000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>18890000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>2277000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bunyodkor Agro MChJ</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>339582386</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000827017344001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2614</t>
+          <t>Оплата за товар по счет-фактуре №5961 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>148271000</v>
+        <v>147246000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>39575000</v>
+        <v>16000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4267</t>
+          <t>Tovarlar uchun to'lov h/f №5352</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>108696000</v>
+        <v>147230000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>16213000</v>
+        <v>34509000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5366,317 +5376,307 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №129/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №3/26 от 03.09.2026</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>124909000</v>
+        <v>181739000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>1587000</v>
+        <v>1306000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1830 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №4123 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>126496000</v>
+        <v>183045000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>7495000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>819000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish AJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>271750547</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000141629067001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №71/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №34/26</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>133991000</v>
+        <v>182226000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>3658000</v>
+        <v>7708000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №4596 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Mahsulot uchun to'lov, shartnoma №160/26, QQS 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>137649000</v>
+        <v>189934000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>1557000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>91000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mehnat Qurilish AJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>271750547</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000141629067001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2352</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №102/26</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>139206000</v>
+        <v>189843000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46279</v>
+        <v>46270</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>1769000</v>
+        <v>23600000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4118)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000357876854417</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Kredit shartnomasi L-2025-4118 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>137437000</v>
+        <v>166243000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>1769000</v>
+        <v>12971000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №5510</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>135668000</v>
+        <v>153272000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>8656000</v>
+        <v>154876000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Yangi Hayot Poligraf XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>235008991</t>
+          <t>371671734</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000299291143001</t>
+          <t>20208000910587057001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №239/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №6234</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>127012000</v>
+        <v>-1604000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>20873000</v>
+        <v>1446000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shahrisabz Farm Savdo MChJ</t>
+          <t>Mehnat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>235008991</t>
+          <t>247765290</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000299291143001</t>
+          <t>20208000806392850001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5686,277 +5686,277 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №283/26</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №93/21</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>106139000</v>
+        <v>-3050000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>3652000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>9769000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Shodlik Yog' Zavodi AJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>335966150</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000634290403001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1499</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3786 09.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>102487000</v>
+        <v>6719000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>6633000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>5408000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Shodlik Yog' Zavodi AJ</t>
+          <t>Qarshi Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>335966150</t>
+          <t>219709254</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000634290403001</t>
+          <t>20208000467013464001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6953</t>
+          <t>Оплата по счет-фактуре №7151 за поставленный товар</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>95854000</v>
+        <v>12127000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>3340000</v>
+        <v>62707000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Guliston Agro MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>347392767</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000366955723001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №51/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №322 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>99194000</v>
+        <v>74834000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>17344000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>8444000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Barakali Trans Servis AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>341565273</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000086768431001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6008</t>
+          <t>Предоплата за товар по дог. №15/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>81850000</v>
+        <v>83278000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>5870000</v>
+        <v>7660000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bog'ishamol Trans Servis MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>310010115</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000377800474001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплатапо счет-фактуре №6319 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9048 ОТ 14.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>87720000</v>
+        <v>90938000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>2813000</v>
+        <v>3298000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mehnat Dori-Darmon XK</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>294197092</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000434670134001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shartnoma №160/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4243 ОТ 14.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>90533000</v>
+        <v>94236000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>1921000</v>
+        <v>1456000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5966,77 +5966,77 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №503 за поставленный товар</t>
+          <t>Предоплата за товар по договору №74/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>92454000</v>
+        <v>95692000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>2426000</v>
+        <v>10000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Yangi Hayot Poligraf XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>371671734</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000910587057001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №7861</t>
+          <t>Предоплата за материалы по договору №239/26</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>90028000</v>
+        <v>95682000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>35264000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Lazzat Tekstil AJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>395020603</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000998093109001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6046,237 +6046,237 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2559 21.09.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №16/26, QQS bilan</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>125292000</v>
+        <v>95666000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>2547000</v>
+        <v>16000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bunyodkor Agro MChJ</t>
+          <t>Kamalak Poligraf XK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>339582386</t>
+          <t>214497709</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000827017344001</t>
+          <t>20208000139116837001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №3/26 от 21.09.2026, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №166/26</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>122745000</v>
+        <v>95650000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>5489000</v>
+        <v>22000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bahor Sut Mahsulotlari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>217610019</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000139922512001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8760</t>
+          <t>Оплата за сырье по дог. №266/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>117256000</v>
+        <v>95628000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>2411000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>3941000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Оплата по с/ф №3219 за поставленный товар</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>114845000</v>
+        <v>99569000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>3714000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>1366000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Shodlik Yog' Zavodi AJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>335966150</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000634290403001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №240/26, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №31/26, НДС 12%</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>111131000</v>
+        <v>100935000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>6165000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>339113949</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000809924118001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №8573 ОТ 23.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3750</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>117296000</v>
+        <v>100926000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>10808000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Denov Yog'och XK</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>220309514</t>
+          <t>386024623</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000994887299001</t>
+          <t>20208000469735206001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6286,311 +6286,1031 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №111/26 от 24.09.2026</t>
+          <t>Предоплата за материалы по договору №26/26</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>128104000</v>
+        <v>100891000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>3329000</v>
+        <v>1769000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Omad Yog'och MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>268214926</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000352537634001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №268/26</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>124775000</v>
+        <v>99122000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46290</v>
+        <v>46280</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>1524000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>1769000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №33/26 от 25.09.2026</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>126299000</v>
+        <v>97353000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>12004000</v>
+        <v>8369000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>230951489</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000488729946001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5424 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №104/26, НДС 12%</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>138303000</v>
+        <v>105722000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>2069000</v>
+        <v>1303000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №543 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №155/26, НДС 12%</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>140372000</v>
+        <v>107025000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>904000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>1252000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201011503</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000087743622001</t>
+          <t>20208000780047456001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за продукцию по дог. №141/26, НДС 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>139468000</v>
+        <v>108277000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>1632000</v>
+        <v>7997000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Olmaliq Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Metall Servis XK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>387415652</t>
+          <t>275054751</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000330867684001</t>
+          <t>20208000162906771001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Shartnoma №278/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №9758 от 18.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>141100000</v>
+        <v>116274000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46295</v>
+        <v>46283</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Qarshi Farm Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>219709254</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000467013464001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Shartnoma №43/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>117754000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>5677000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Barakali Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>341565273</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000086768431001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №3622 от 21.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>123431000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>2208000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Barakali Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>341565273</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000086768431001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №116/26 от 21.09.2026</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>125639000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>17000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Omad Agro MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>358238658</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000701734430001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №85/26</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>125622000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Denov Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>391515743</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000948597057001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №91/26</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>125572000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>1395000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Denov Metall Servis XK</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>275054751</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000162906771001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №112/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>126967000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>1267000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Denov Metall Servis XK</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>275054751</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000162906771001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Shartnoma №20026 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>128234000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Omad Agro MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>358238658</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000701734430001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №4792</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>128198000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>2134000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Denov Metall Servis XK</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>275054751</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000162906771001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №2933 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>130332000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>2422000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>127910000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>185000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Omad Agro MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>358238658</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000701734430001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №298/26</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>127725000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>904000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000814682149001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>126821000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>4654000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Olmaliq Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>230951489</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000488729946001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>TOVAR UCHUN TO'LOV, H/F №3552 28.09.2026, QQS BILAN</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>131475000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>4380000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Barakali Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>341565273</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000086768431001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №7875 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>135855000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Yangi Hayot Poligraf XK</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>371671734</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000910587057001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №293/26 от 28.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>135833000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>1859000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Denov Metall Servis XK</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>275054751</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000162906771001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №267/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>137692000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>1671000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Qarshi Farm Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>219709254</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000467013464001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №7/26 от 29.09.2026</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>139363000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Barakali Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>341565273</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000086768431001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №113/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>141100000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
         <is>
           <t>Navbahor Bank ATB</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>01121</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Плата за SMS-информирование</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
         <v>140800000</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C160" s="4" t="n">
-        <v>609917000</v>
-      </c>
-      <c r="D160" s="4" t="n">
-        <v>608017000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="C178" s="4" t="n">
+        <v>609563000</v>
+      </c>
+      <c r="D178" s="4" t="n">
+        <v>607663000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C161" s="4" t="n">
+      <c r="C179" s="4" t="n">
         <v>140800000</v>
       </c>
-      <c r="D161" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
